--- a/oPool_display/experimental_data/validation/ELISA/ELISA_Validation_Results.xlsx
+++ b/oPool_display/experimental_data/validation/ELISA/ELISA_Validation_Results.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/owenouyang/Desktop/Git_Repo/oPool/result/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/owenouyang/Desktop/Git_Repo/oPool_display/oPool_display/experimental_data/validation/ELISA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4412D6BC-6EF7-AE40-8E47-A3B2C1165B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269ED3B4-480E-2D46-B753-E47C7C62D303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42560" yWindow="880" windowWidth="25640" windowHeight="14440" xr2:uid="{7D02DDC7-270D-6943-9D30-F80F18FA5150}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$253</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -54,9 +57,6 @@
   </si>
   <si>
     <t>045-09-1G05</t>
-  </si>
-  <si>
-    <t>C3-2-F02</t>
   </si>
   <si>
     <t>240-14-IgA-2F02</t>
@@ -162,6 +162,9 @@
   </si>
   <si>
     <t>Antibody</t>
+  </si>
+  <si>
+    <t>C3-2-3F02</t>
   </si>
 </sst>
 </file>
@@ -815,7 +818,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -827,7 +830,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -835,7 +838,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1">
         <v>1.1950000000000001</v>
@@ -853,7 +856,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3">
         <v>1.6140000000000001</v>
@@ -871,7 +874,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="4">
         <v>7.8E-2</v>
@@ -886,10 +889,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4">
         <v>0.17699999999999999</v>
@@ -904,10 +907,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4">
         <v>7.0999999999999994E-2</v>
@@ -922,10 +925,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4">
         <v>0.09</v>
@@ -940,10 +943,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4">
         <v>0.14199999999999999</v>
@@ -958,10 +961,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="5">
         <v>0.09</v>
@@ -976,10 +979,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4">
         <v>7.8E-2</v>
@@ -994,10 +997,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="4">
         <v>7.3999999999999996E-2</v>
@@ -1012,10 +1015,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4">
         <v>7.0999999999999994E-2</v>
@@ -1030,10 +1033,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="7">
         <v>1.9059999999999999</v>
@@ -1048,10 +1051,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="4">
         <v>0.121</v>
@@ -1066,10 +1069,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="5">
         <v>7.3999999999999996E-2</v>
@@ -1084,10 +1087,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="4">
         <v>0.09</v>
@@ -1102,10 +1105,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="2">
         <v>1.8220000000000001</v>
@@ -1120,10 +1123,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="4">
         <v>7.3999999999999996E-2</v>
@@ -1138,10 +1141,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="4">
         <v>0.13</v>
@@ -1156,10 +1159,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="4">
         <v>9.4E-2</v>
@@ -1174,10 +1177,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="4">
         <v>7.2999999999999995E-2</v>
@@ -1192,10 +1195,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="4">
         <v>9.9000000000000005E-2</v>
@@ -1210,10 +1213,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="4">
         <v>6.7000000000000004E-2</v>
@@ -1228,10 +1231,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="4">
         <v>9.8000000000000004E-2</v>
@@ -1246,10 +1249,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="5">
         <v>0.10100000000000001</v>
@@ -1264,10 +1267,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
         <v>27</v>
-      </c>
-      <c r="B26" t="s">
-        <v>28</v>
       </c>
       <c r="C26" s="5">
         <v>0.108</v>
@@ -1282,10 +1285,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="19">
         <v>0.432</v>
@@ -1300,10 +1303,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="7">
         <v>1.988</v>
@@ -1318,10 +1321,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="4">
         <v>7.0000000000000007E-2</v>
@@ -1339,7 +1342,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30" s="8">
         <v>1.4890000000000001</v>
@@ -1357,7 +1360,7 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C31" s="4">
         <v>0.104</v>
@@ -1375,7 +1378,7 @@
         <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C32" s="5">
         <v>8.3000000000000004E-2</v>
@@ -1390,10 +1393,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C33" s="4">
         <v>7.6999999999999999E-2</v>
@@ -1408,10 +1411,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" s="9">
         <v>2.1320000000000001</v>
@@ -1426,10 +1429,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C35" s="2">
         <v>1.702</v>
@@ -1444,10 +1447,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" s="2">
         <v>1.726</v>
@@ -1462,10 +1465,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C37" s="10">
         <v>2.0659999999999998</v>
@@ -1480,10 +1483,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C38" s="4">
         <v>7.8E-2</v>
@@ -1498,10 +1501,10 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C39" s="4">
         <v>7.5999999999999998E-2</v>
@@ -1516,10 +1519,10 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C40" s="4">
         <v>8.1000000000000003E-2</v>
@@ -1534,10 +1537,10 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C41" s="12">
         <v>0.23499999999999999</v>
@@ -1552,10 +1555,10 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42" s="13">
         <v>0.26600000000000001</v>
@@ -1570,10 +1573,10 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C43" s="4">
         <v>0.123</v>
@@ -1588,10 +1591,10 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C44" s="5">
         <v>0.14799999999999999</v>
@@ -1606,10 +1609,10 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C45" s="4">
         <v>0.16400000000000001</v>
@@ -1624,10 +1627,10 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C46" s="4">
         <v>0.11</v>
@@ -1642,10 +1645,10 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C47" s="4">
         <v>0.17899999999999999</v>
@@ -1660,10 +1663,10 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C48" s="14">
         <v>0.13700000000000001</v>
@@ -1678,10 +1681,10 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C49" s="5">
         <v>8.6999999999999994E-2</v>
@@ -1696,10 +1699,10 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C50" s="14">
         <v>0.114</v>
@@ -1714,10 +1717,10 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C51" s="14">
         <v>7.6999999999999999E-2</v>
@@ -1732,10 +1735,10 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C52" s="14">
         <v>9.9000000000000005E-2</v>
@@ -1750,10 +1753,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C53" s="5">
         <v>0.111</v>
@@ -1768,10 +1771,10 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C54" s="14">
         <v>8.5999999999999993E-2</v>
@@ -1786,10 +1789,10 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C55" s="15">
         <v>1.992</v>
@@ -1804,10 +1807,10 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C56" s="17">
         <v>0.61899999999999999</v>
@@ -1822,10 +1825,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C57" s="5">
         <v>7.2999999999999995E-2</v>
@@ -1843,7 +1846,7 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C58" s="20">
         <v>1.5249999999999999</v>
@@ -1861,7 +1864,7 @@
         <v>4</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" s="22">
         <v>1.49</v>
@@ -1879,7 +1882,7 @@
         <v>5</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C60" s="24">
         <v>1.3480000000000001</v>
@@ -1894,10 +1897,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C61" s="14">
         <v>0.13500000000000001</v>
@@ -1912,10 +1915,10 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C62" s="25">
         <v>0.66300000000000003</v>
@@ -1930,10 +1933,10 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C63" s="14">
         <v>0.121</v>
@@ -1948,10 +1951,10 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C64" s="5">
         <v>0.16400000000000001</v>
@@ -1966,10 +1969,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C65" s="14">
         <v>0.14099999999999999</v>
@@ -1984,10 +1987,10 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C66" s="24">
         <v>1.357</v>
@@ -2002,10 +2005,10 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C67" s="24">
         <v>1.3939999999999999</v>
@@ -2020,10 +2023,10 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C68" s="33">
         <v>2.3849999999999998</v>
@@ -2038,10 +2041,10 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C69" s="24">
         <v>1.383</v>
@@ -2056,10 +2059,10 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C70" s="14">
         <v>0.17100000000000001</v>
@@ -2074,10 +2077,10 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B71" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C71" s="15">
         <v>1.8740000000000001</v>
@@ -2092,10 +2095,10 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C72" s="24">
         <v>1.431</v>
@@ -2110,10 +2113,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C73" s="24">
         <v>1.4359999999999999</v>
@@ -2128,10 +2131,10 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C74" s="5">
         <v>0.10199999999999999</v>
@@ -2146,10 +2149,10 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C75" s="28">
         <v>0.20799999999999999</v>
@@ -2164,10 +2167,10 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B76" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C76" s="24">
         <v>1.44</v>
@@ -2182,10 +2185,10 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C77" s="5">
         <v>0.11799999999999999</v>
@@ -2200,10 +2203,10 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C78" s="14">
         <v>0.124</v>
@@ -2218,10 +2221,10 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B79" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C79" s="14">
         <v>0.111</v>
@@ -2236,10 +2239,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C80" s="14">
         <v>0.114</v>
@@ -2254,10 +2257,10 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C81" s="24">
         <v>1.329</v>
@@ -2272,10 +2275,10 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C82" s="14">
         <v>0.121</v>
@@ -2290,10 +2293,10 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" t="s">
         <v>31</v>
-      </c>
-      <c r="B83" t="s">
-        <v>32</v>
       </c>
       <c r="C83" s="29">
         <v>0.35499999999999998</v>
@@ -2308,10 +2311,10 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B84" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C84" s="24">
         <v>1.3320000000000001</v>
@@ -2326,10 +2329,10 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B85" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C85" s="29">
         <v>0.46</v>
@@ -2347,7 +2350,7 @@
         <v>3</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C86" s="23">
         <v>1.591</v>
@@ -2365,7 +2368,7 @@
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C87" s="20">
         <v>1.573</v>
@@ -2383,7 +2386,7 @@
         <v>5</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C88" s="22">
         <v>1.51</v>
@@ -2398,10 +2401,10 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C89" s="13">
         <v>0.317</v>
@@ -2416,10 +2419,10 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C90" s="14">
         <v>0.20100000000000001</v>
@@ -2434,10 +2437,10 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C91" s="5">
         <v>0.16</v>
@@ -2452,10 +2455,10 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C92" s="14">
         <v>0.14799999999999999</v>
@@ -2470,10 +2473,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C93" s="14">
         <v>0.14399999999999999</v>
@@ -2488,10 +2491,10 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C94" s="22">
         <v>1.615</v>
@@ -2506,10 +2509,10 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C95" s="22">
         <v>1.5820000000000001</v>
@@ -2524,10 +2527,10 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C96" s="33">
         <v>2.4009999999999998</v>
@@ -2542,10 +2545,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C97" s="24">
         <v>1.504</v>
@@ -2560,10 +2563,10 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C98" s="14">
         <v>0.13200000000000001</v>
@@ -2578,10 +2581,10 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C99" s="17">
         <v>0.73</v>
@@ -2596,10 +2599,10 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C100" s="23">
         <v>1.6950000000000001</v>
@@ -2614,10 +2617,10 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C101" s="23">
         <v>1.732</v>
@@ -2632,10 +2635,10 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C102" s="14">
         <v>9.6000000000000002E-2</v>
@@ -2650,10 +2653,10 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C103" s="14">
         <v>0.11899999999999999</v>
@@ -2668,10 +2671,10 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C104" s="23">
         <v>1.728</v>
@@ -2686,10 +2689,10 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C105" s="14">
         <v>0.11700000000000001</v>
@@ -2704,10 +2707,10 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C106" s="14">
         <v>0.108</v>
@@ -2722,10 +2725,10 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C107" s="14">
         <v>9.4E-2</v>
@@ -2740,10 +2743,10 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C108" s="5">
         <v>0.10299999999999999</v>
@@ -2758,10 +2761,10 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C109" s="22">
         <v>1.601</v>
@@ -2776,10 +2779,10 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C110" s="14">
         <v>9.8000000000000004E-2</v>
@@ -2794,10 +2797,10 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C111" s="28">
         <v>0.32800000000000001</v>
@@ -2812,10 +2815,10 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C112" s="23">
         <v>1.8</v>
@@ -2830,10 +2833,10 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
+        <v>32</v>
+      </c>
+      <c r="B113" t="s">
         <v>33</v>
-      </c>
-      <c r="B113" t="s">
-        <v>34</v>
       </c>
       <c r="C113" s="14">
         <v>9.5000000000000001E-2</v>
@@ -2851,7 +2854,7 @@
         <v>3</v>
       </c>
       <c r="B114" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C114" s="33">
         <v>1.9</v>
@@ -2869,7 +2872,7 @@
         <v>4</v>
       </c>
       <c r="B115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C115" s="5">
         <v>8.5999999999999993E-2</v>
@@ -2887,7 +2890,7 @@
         <v>5</v>
       </c>
       <c r="B116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C116" s="22">
         <v>1.5249999999999999</v>
@@ -2902,10 +2905,10 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B117" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C117" s="14">
         <v>8.1000000000000003E-2</v>
@@ -2920,10 +2923,10 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B118" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C118" s="24">
         <v>1.415</v>
@@ -2938,10 +2941,10 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C119" s="35">
         <v>1.165</v>
@@ -2956,10 +2959,10 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C120" s="16">
         <v>1.891</v>
@@ -2974,10 +2977,10 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C121" s="24">
         <v>1.49</v>
@@ -2992,10 +2995,10 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B122" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C122" s="14">
         <v>9.6000000000000002E-2</v>
@@ -3010,10 +3013,10 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C123" s="14">
         <v>8.6999999999999994E-2</v>
@@ -3028,10 +3031,10 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C124" s="14">
         <v>8.6999999999999994E-2</v>
@@ -3046,10 +3049,10 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B125" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C125" s="14">
         <v>0.155</v>
@@ -3064,10 +3067,10 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C126" s="14">
         <v>0.17499999999999999</v>
@@ -3082,10 +3085,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C127" s="22">
         <v>1.607</v>
@@ -3100,10 +3103,10 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B128" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C128" s="14">
         <v>0.108</v>
@@ -3118,10 +3121,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C129" s="14">
         <v>0.111</v>
@@ -3136,10 +3139,10 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C130" s="14">
         <v>0.104</v>
@@ -3154,10 +3157,10 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B131" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C131" s="14">
         <v>0.115</v>
@@ -3172,10 +3175,10 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B132" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C132" s="15">
         <v>2.0920000000000001</v>
@@ -3190,10 +3193,10 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B133" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C133" s="14">
         <v>0.13600000000000001</v>
@@ -3208,10 +3211,10 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B134" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C134" s="5">
         <v>0.122</v>
@@ -3226,10 +3229,10 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B135" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C135" s="14">
         <v>0.105</v>
@@ -3244,10 +3247,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B136" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C136" s="14">
         <v>0.13600000000000001</v>
@@ -3262,10 +3265,10 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B137" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C137" s="24">
         <v>1.415</v>
@@ -3280,10 +3283,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B138" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C138" s="14">
         <v>0.112</v>
@@ -3298,10 +3301,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B139" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C139" s="28">
         <v>0.23699999999999999</v>
@@ -3316,10 +3319,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B140" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C140" s="28">
         <v>0.28599999999999998</v>
@@ -3334,10 +3337,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B141" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C141" s="14">
         <v>0.105</v>
@@ -3355,7 +3358,7 @@
         <v>3</v>
       </c>
       <c r="B142" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C142" s="28">
         <v>0.245</v>
@@ -3373,7 +3376,7 @@
         <v>4</v>
       </c>
       <c r="B143" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C143" s="14">
         <v>0.16400000000000001</v>
@@ -3391,7 +3394,7 @@
         <v>5</v>
       </c>
       <c r="B144" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C144" s="23">
         <v>1.528</v>
@@ -3406,10 +3409,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B145" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C145" s="14">
         <v>0.09</v>
@@ -3424,10 +3427,10 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C146" s="14">
         <v>0.104</v>
@@ -3442,10 +3445,10 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C147" s="14">
         <v>0.09</v>
@@ -3460,10 +3463,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B148" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C148" s="14">
         <v>0.13</v>
@@ -3478,10 +3481,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B149" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C149" s="14">
         <v>9.8000000000000004E-2</v>
@@ -3496,10 +3499,10 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B150" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C150" s="28">
         <v>0.26900000000000002</v>
@@ -3514,10 +3517,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B151" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C151" s="14">
         <v>0.184</v>
@@ -3532,10 +3535,10 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C152" s="14">
         <v>0.108</v>
@@ -3550,10 +3553,10 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B153" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C153" s="37">
         <v>0.33500000000000002</v>
@@ -3568,10 +3571,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B154" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C154" s="14">
         <v>0.105</v>
@@ -3586,10 +3589,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C155" s="22">
         <v>1.3660000000000001</v>
@@ -3604,10 +3607,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C156" s="28">
         <v>0.26500000000000001</v>
@@ -3622,10 +3625,10 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B157" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C157" s="16">
         <v>1.554</v>
@@ -3640,10 +3643,10 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B158" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C158" s="14">
         <v>9.0999999999999998E-2</v>
@@ -3658,10 +3661,10 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B159" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C159" s="14">
         <v>9.9000000000000005E-2</v>
@@ -3676,10 +3679,10 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B160" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C160" s="14">
         <v>0.105</v>
@@ -3694,10 +3697,10 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B161" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C161" s="14">
         <v>9.2999999999999999E-2</v>
@@ -3712,10 +3715,10 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B162" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C162" s="15">
         <v>1.6719999999999999</v>
@@ -3730,10 +3733,10 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B163" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C163" s="14">
         <v>8.7999999999999995E-2</v>
@@ -3748,10 +3751,10 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B164" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C164" s="14">
         <v>8.8999999999999996E-2</v>
@@ -3766,10 +3769,10 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B165" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C165" s="14">
         <v>0.109</v>
@@ -3784,10 +3787,10 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B166" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C166" s="14">
         <v>9.0999999999999998E-2</v>
@@ -3802,10 +3805,10 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B167" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C167" s="14">
         <v>0.11899999999999999</v>
@@ -3820,10 +3823,10 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B168" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C168" s="28">
         <v>0.25900000000000001</v>
@@ -3838,10 +3841,10 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B169" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C169" s="14">
         <v>8.4000000000000005E-2</v>
@@ -3859,7 +3862,7 @@
         <v>3</v>
       </c>
       <c r="B170" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C170" s="28">
         <v>0.23100000000000001</v>
@@ -3877,7 +3880,7 @@
         <v>4</v>
       </c>
       <c r="B171" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C171" s="14">
         <v>9.5000000000000001E-2</v>
@@ -3895,7 +3898,7 @@
         <v>5</v>
       </c>
       <c r="B172" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C172" s="15">
         <v>1.776</v>
@@ -3910,10 +3913,10 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B173" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C173" s="14">
         <v>8.5000000000000006E-2</v>
@@ -3928,10 +3931,10 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C174" s="14">
         <v>0.106</v>
@@ -3946,10 +3949,10 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B175" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C175" s="14">
         <v>0.10299999999999999</v>
@@ -3964,10 +3967,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C176" s="28">
         <v>0.216</v>
@@ -3982,10 +3985,10 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B177" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C177" s="18">
         <v>0.52300000000000002</v>
@@ -4000,10 +4003,10 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B178" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C178" s="14">
         <v>0.11899999999999999</v>
@@ -4018,10 +4021,10 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B179" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C179" s="14">
         <v>0.11700000000000001</v>
@@ -4036,10 +4039,10 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C180" s="14">
         <v>0.11</v>
@@ -4054,10 +4057,10 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B181" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C181" s="28">
         <v>0.20499999999999999</v>
@@ -4072,10 +4075,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B182" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C182" s="14">
         <v>0.192</v>
@@ -4090,10 +4093,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C183" s="14">
         <v>0.14699999999999999</v>
@@ -4108,10 +4111,10 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B184" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C184" s="14">
         <v>0.13500000000000001</v>
@@ -4126,10 +4129,10 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B185" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C185" s="14">
         <v>0.128</v>
@@ -4144,10 +4147,10 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B186" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C186" s="14">
         <v>9.6000000000000002E-2</v>
@@ -4162,10 +4165,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B187" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C187" s="14">
         <v>0.108</v>
@@ -4180,10 +4183,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B188" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C188" s="15">
         <v>1.8260000000000001</v>
@@ -4198,10 +4201,10 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B189" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C189" s="14">
         <v>9.5000000000000001E-2</v>
@@ -4216,10 +4219,10 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B190" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C190" s="14">
         <v>8.5999999999999993E-2</v>
@@ -4234,10 +4237,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B191" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C191" s="14">
         <v>7.2999999999999995E-2</v>
@@ -4252,10 +4255,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B192" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C192" s="14">
         <v>8.3000000000000004E-2</v>
@@ -4270,10 +4273,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B193" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C193" s="15">
         <v>1.7310000000000001</v>
@@ -4288,10 +4291,10 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B194" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C194" s="14">
         <v>7.8E-2</v>
@@ -4306,10 +4309,10 @@
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B195" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C195" s="14">
         <v>0.13500000000000001</v>
@@ -4324,10 +4327,10 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B196" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C196" s="28">
         <v>0.218</v>
@@ -4342,10 +4345,10 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B197" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C197" s="14">
         <v>8.2000000000000003E-2</v>
@@ -4363,7 +4366,7 @@
         <v>3</v>
       </c>
       <c r="B198" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C198" s="28">
         <v>0.28199999999999997</v>
@@ -4381,7 +4384,7 @@
         <v>4</v>
       </c>
       <c r="B199" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C199" s="14">
         <v>0.13100000000000001</v>
@@ -4399,7 +4402,7 @@
         <v>5</v>
       </c>
       <c r="B200" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C200" s="14">
         <v>0.126</v>
@@ -4414,10 +4417,10 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B201" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C201" s="14">
         <v>0.12</v>
@@ -4432,10 +4435,10 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B202" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C202" s="14">
         <v>0.11700000000000001</v>
@@ -4450,10 +4453,10 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B203" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C203" s="14">
         <v>0.112</v>
@@ -4468,10 +4471,10 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B204" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C204" s="14">
         <v>0.153</v>
@@ -4486,10 +4489,10 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B205" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C205" s="14">
         <v>0.13900000000000001</v>
@@ -4504,10 +4507,10 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B206" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C206" s="14">
         <v>0.115</v>
@@ -4522,10 +4525,10 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B207" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C207" s="14">
         <v>0.106</v>
@@ -4540,10 +4543,10 @@
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C208" s="14">
         <v>0.121</v>
@@ -4558,10 +4561,10 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B209" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C209" s="14">
         <v>0.14699999999999999</v>
@@ -4576,10 +4579,10 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B210" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C210" s="15">
         <v>1.68</v>
@@ -4594,10 +4597,10 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B211" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C211" s="14">
         <v>0.13800000000000001</v>
@@ -4612,10 +4615,10 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C212" s="14">
         <v>0.15</v>
@@ -4630,10 +4633,10 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B213" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C213" s="14">
         <v>0.14199999999999999</v>
@@ -4648,10 +4651,10 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B214" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C214" s="23">
         <v>1.4059999999999999</v>
@@ -4666,10 +4669,10 @@
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B215" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C215" s="23">
         <v>1.429</v>
@@ -4684,10 +4687,10 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B216" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C216" s="28">
         <v>0.215</v>
@@ -4702,10 +4705,10 @@
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B217" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C217" s="16">
         <v>1.516</v>
@@ -4720,10 +4723,10 @@
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B218" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C218" s="14">
         <v>0.154</v>
@@ -4738,10 +4741,10 @@
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B219" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C219" s="15">
         <v>1.671</v>
@@ -4756,10 +4759,10 @@
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B220" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C220" s="22">
         <v>1.2709999999999999</v>
@@ -4774,10 +4777,10 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B221" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C221" s="14">
         <v>0.16300000000000001</v>
@@ -4792,10 +4795,10 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B222" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C222" s="27">
         <v>1.03</v>
@@ -4810,10 +4813,10 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B223" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C223" s="28">
         <v>0.22800000000000001</v>
@@ -4828,10 +4831,10 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B224" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C224" s="22">
         <v>1.2949999999999999</v>
@@ -4846,10 +4849,10 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B225" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C225" s="14">
         <v>0.13400000000000001</v>
@@ -4867,7 +4870,7 @@
         <v>3</v>
       </c>
       <c r="B226" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C226" s="13">
         <v>0.29099999999999998</v>
@@ -4885,7 +4888,7 @@
         <v>4</v>
       </c>
       <c r="B227" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C227" s="14">
         <v>0.10299999999999999</v>
@@ -4903,7 +4906,7 @@
         <v>5</v>
       </c>
       <c r="B228" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C228" s="14">
         <v>0.189</v>
@@ -4918,10 +4921,10 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="B229" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C229" s="14">
         <v>9.0999999999999998E-2</v>
@@ -4936,10 +4939,10 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B230" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C230" s="14">
         <v>0.13200000000000001</v>
@@ -4954,10 +4957,10 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B231" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C231" s="14">
         <v>0.121</v>
@@ -4972,10 +4975,10 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B232" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C232" s="28">
         <v>0.19700000000000001</v>
@@ -4990,10 +4993,10 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B233" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C233" s="14">
         <v>0.13400000000000001</v>
@@ -5008,10 +5011,10 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B234" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C234" s="14">
         <v>0.112</v>
@@ -5026,10 +5029,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B235" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C235" s="14">
         <v>0.16600000000000001</v>
@@ -5044,10 +5047,10 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C236" s="14">
         <v>0.107</v>
@@ -5062,10 +5065,10 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B237" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C237" s="14">
         <v>0.14699999999999999</v>
@@ -5080,10 +5083,10 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B238" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C238" s="14">
         <v>0.18</v>
@@ -5098,10 +5101,10 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B239" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C239" s="5">
         <v>0.17100000000000001</v>
@@ -5116,10 +5119,10 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C240" s="14">
         <v>0.13500000000000001</v>
@@ -5134,10 +5137,10 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B241" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C241" s="28">
         <v>0.24</v>
@@ -5152,10 +5155,10 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B242" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C242" s="23">
         <v>1.472</v>
@@ -5170,10 +5173,10 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B243" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C243" s="22">
         <v>1.3779999999999999</v>
@@ -5188,10 +5191,10 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B244" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C244" s="28">
         <v>0.23599999999999999</v>
@@ -5206,10 +5209,10 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B245" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C245" s="17">
         <v>0.67100000000000004</v>
@@ -5224,10 +5227,10 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B246" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C246" s="14">
         <v>0.11899999999999999</v>
@@ -5242,10 +5245,10 @@
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B247" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C247" s="16">
         <v>1.64</v>
@@ -5260,10 +5263,10 @@
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B248" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C248" s="14">
         <v>0.13200000000000001</v>
@@ -5278,10 +5281,10 @@
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B249" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C249" s="28">
         <v>0.23899999999999999</v>
@@ -5296,10 +5299,10 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B250" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C250" s="22">
         <v>1.4259999999999999</v>
@@ -5314,10 +5317,10 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B251" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C251" s="28">
         <v>0.24099999999999999</v>
@@ -5332,10 +5335,10 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B252" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C252" s="15">
         <v>1.7709999999999999</v>
@@ -5350,10 +5353,10 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B253" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C253" s="14">
         <v>0.14499999999999999</v>
@@ -5367,6 +5370,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E253" xr:uid="{BF2D7733-02BD-F345-959A-248EF3060234}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
